--- a/data/volatility/Bitcoin Volatility.xlsx
+++ b/data/volatility/Bitcoin Volatility.xlsx
@@ -1,37 +1,92 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\volatility\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75DF5D4F-824F-44E6-9A30-7212CCBA8DF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="BITVX" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+  <si>
+    <t>close</t>
+  </si>
+  <si>
+    <t>high</t>
+  </si>
+  <si>
+    <t>low</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Time</t>
+  </si>
+  <si>
+    <t>Time Zone</t>
+  </si>
+  <si>
+    <t>Base Date</t>
+  </si>
+  <si>
+    <t>Release Date</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="3">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,85 +101,37 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="2">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -412,987 +419,1344 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F48"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H48"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10.08984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.54296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.08984375" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.453125" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="8" width="8.7265625" style="4"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>datetime</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>close</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>volume</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="n">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" s="2">
         <v>46105</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="2">
+        <v>46105</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="D2" s="2" t="str">
+        <f>IF(
+ AND(
+  B2 &gt;= IF(
+         YEAR(B2)&gt;=2007,
+         DATE(YEAR(B2),3,14)-WEEKDAY(DATE(YEAR(B2),3,14),1)+1 + TIME(2,0,0),
+         DATE(YEAR(B2),4,7)-WEEKDAY(DATE(YEAR(B2),4,7),1)+1 + TIME(2,0,0)
+       ),
+  B2 &lt;  IF(
+         YEAR(B2)&gt;=2007,
+         DATE(YEAR(B2),11,7)-WEEKDAY(DATE(YEAR(B2),11,7),1)+1 + TIME(2,0,0),
+         DATE(YEAR(B2),10,31)-WEEKDAY(DATE(YEAR(B2),10,31),1) + TIME(2,0,0)
+       )
+ ),
+ "UTC-4",
+ "UTC-5"
+)</f>
+        <v>UTC-4</v>
+      </c>
+      <c r="E2" s="4">
         <v>58.45</v>
       </c>
-      <c r="C2" t="n">
+      <c r="F2" s="4">
         <v>59.29</v>
       </c>
-      <c r="D2" t="n">
+      <c r="G2" s="4">
         <v>58.01</v>
       </c>
-      <c r="E2" t="n">
+      <c r="H2" s="4">
         <v>58.04</v>
       </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" s="2">
         <v>46106</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="2">
+        <v>46106</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="D3" s="2" t="str">
+        <f t="shared" ref="D3:D48" si="0">IF(
+ AND(
+  B3 &gt;= IF(
+         YEAR(B3)&gt;=2007,
+         DATE(YEAR(B3),3,14)-WEEKDAY(DATE(YEAR(B3),3,14),1)+1 + TIME(2,0,0),
+         DATE(YEAR(B3),4,7)-WEEKDAY(DATE(YEAR(B3),4,7),1)+1 + TIME(2,0,0)
+       ),
+  B3 &lt;  IF(
+         YEAR(B3)&gt;=2007,
+         DATE(YEAR(B3),11,7)-WEEKDAY(DATE(YEAR(B3),11,7),1)+1 + TIME(2,0,0),
+         DATE(YEAR(B3),10,31)-WEEKDAY(DATE(YEAR(B3),10,31),1) + TIME(2,0,0)
+       )
+ ),
+ "UTC-4",
+ "UTC-5"
+)</f>
+        <v>UTC-4</v>
+      </c>
+      <c r="E3" s="4">
         <v>56.02</v>
       </c>
-      <c r="C3" t="n">
+      <c r="F3" s="4">
         <v>57</v>
       </c>
-      <c r="D3" t="n">
+      <c r="G3" s="4">
         <v>55.92</v>
       </c>
-      <c r="E3" t="n">
+      <c r="H3" s="4">
         <v>56.75</v>
       </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" s="2">
         <v>46107</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="2">
+        <v>46107</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="D4" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E4" s="4">
         <v>58.18</v>
       </c>
-      <c r="C4" t="n">
+      <c r="F4" s="4">
         <v>58.52</v>
       </c>
-      <c r="D4" t="n">
+      <c r="G4" s="4">
         <v>56.56</v>
       </c>
-      <c r="E4" t="n">
+      <c r="H4" s="4">
         <v>57.12</v>
       </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" s="2">
         <v>46108</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="2">
+        <v>46108</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="D5" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E5" s="4">
         <v>60.37</v>
       </c>
-      <c r="C5" t="n">
+      <c r="F5" s="4">
         <v>61.62</v>
       </c>
-      <c r="D5" t="n">
+      <c r="G5" s="4">
         <v>60.11</v>
       </c>
-      <c r="E5" t="n">
+      <c r="H5" s="4">
         <v>60.21</v>
       </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" s="2">
         <v>46111</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="2">
+        <v>46111</v>
+      </c>
+      <c r="C6" s="1">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="D6" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E6" s="4">
         <v>60.15</v>
       </c>
-      <c r="C6" t="n">
+      <c r="F6" s="4">
         <v>60.69</v>
       </c>
-      <c r="D6" t="n">
+      <c r="G6" s="4">
         <v>58.15</v>
       </c>
-      <c r="E6" t="n">
+      <c r="H6" s="4">
         <v>59.06</v>
       </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" s="2">
         <v>46112</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="D7" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E7" s="4">
         <v>56.92</v>
       </c>
-      <c r="C7" t="n">
+      <c r="F7" s="4">
         <v>59.83</v>
       </c>
-      <c r="D7" t="n">
+      <c r="G7" s="4">
         <v>56.8</v>
       </c>
-      <c r="E7" t="n">
+      <c r="H7" s="4">
         <v>59.61</v>
       </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" s="2">
         <v>46113</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" s="2">
+        <v>46113</v>
+      </c>
+      <c r="C8" s="1">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="D8" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E8" s="4">
         <v>56.35</v>
       </c>
-      <c r="C8" t="n">
+      <c r="F8" s="4">
         <v>58.74</v>
       </c>
-      <c r="D8" t="n">
+      <c r="G8" s="4">
         <v>55.8</v>
       </c>
-      <c r="E8" t="n">
+      <c r="H8" s="4">
         <v>56.92</v>
       </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" s="2">
         <v>46114</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" s="2">
+        <v>46114</v>
+      </c>
+      <c r="C9" s="1">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="D9" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E9" s="4">
         <v>54.85</v>
       </c>
-      <c r="C9" t="n">
+      <c r="F9" s="4">
         <v>58.56</v>
       </c>
-      <c r="D9" t="n">
+      <c r="G9" s="4">
         <v>54.72</v>
       </c>
-      <c r="E9" t="n">
+      <c r="H9" s="4">
         <v>58.1</v>
       </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" s="2">
         <v>46118</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10" s="2">
+        <v>46118</v>
+      </c>
+      <c r="C10" s="1">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="D10" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E10" s="4">
         <v>52.08</v>
       </c>
-      <c r="C10" t="n">
+      <c r="F10" s="4">
         <v>53.61</v>
       </c>
-      <c r="D10" t="n">
+      <c r="G10" s="4">
         <v>51.85</v>
       </c>
-      <c r="E10" t="n">
+      <c r="H10" s="4">
         <v>53.44</v>
       </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n">
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11" s="2">
         <v>46119</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11" s="2">
+        <v>46119</v>
+      </c>
+      <c r="C11" s="1">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="D11" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E11" s="4">
         <v>54.41</v>
       </c>
-      <c r="C11" t="n">
+      <c r="F11" s="4">
         <v>54.68</v>
       </c>
-      <c r="D11" t="n">
+      <c r="G11" s="4">
         <v>53.31</v>
       </c>
-      <c r="E11" t="n">
+      <c r="H11" s="4">
         <v>53.31</v>
       </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="n">
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" s="2">
         <v>46120</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12" s="2">
+        <v>46120</v>
+      </c>
+      <c r="C12" s="1">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="D12" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E12" s="4">
         <v>49.2</v>
       </c>
-      <c r="C12" t="n">
+      <c r="F12" s="4">
         <v>50.98</v>
       </c>
-      <c r="D12" t="n">
+      <c r="G12" s="4">
         <v>48.85</v>
       </c>
-      <c r="E12" t="n">
+      <c r="H12" s="4">
         <v>49.53</v>
       </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n">
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13" s="2">
         <v>46121</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13" s="2">
+        <v>46121</v>
+      </c>
+      <c r="C13" s="1">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="D13" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E13" s="4">
         <v>48.02</v>
       </c>
-      <c r="C13" t="n">
+      <c r="F13" s="4">
         <v>49.47</v>
       </c>
-      <c r="D13" t="n">
+      <c r="G13" s="4">
         <v>47.68</v>
       </c>
-      <c r="E13" t="n">
+      <c r="H13" s="4">
         <v>49.16</v>
       </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="n">
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14" s="2">
         <v>46122</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" s="2">
+        <v>46122</v>
+      </c>
+      <c r="C14" s="1">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="D14" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E14" s="4">
         <v>46.41</v>
       </c>
-      <c r="C14" t="n">
+      <c r="F14" s="4">
         <v>47.52</v>
       </c>
-      <c r="D14" t="n">
+      <c r="G14" s="4">
         <v>46.39</v>
       </c>
-      <c r="E14" t="n">
+      <c r="H14" s="4">
         <v>47.3</v>
       </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n">
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15" s="2">
         <v>46125</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15" s="2">
+        <v>46125</v>
+      </c>
+      <c r="C15" s="1">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="D15" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E15" s="4">
         <v>48.03</v>
       </c>
-      <c r="C15" t="n">
+      <c r="F15" s="4">
         <v>49.47</v>
       </c>
-      <c r="D15" t="n">
+      <c r="G15" s="4">
         <v>48.01</v>
       </c>
-      <c r="E15" t="n">
+      <c r="H15" s="4">
         <v>48.99</v>
       </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="n">
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A16" s="2">
         <v>46126</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16" s="2">
+        <v>46126</v>
+      </c>
+      <c r="C16" s="1">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="D16" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E16" s="4">
         <v>48.69</v>
       </c>
-      <c r="C16" t="n">
+      <c r="F16" s="4">
         <v>49.93</v>
       </c>
-      <c r="D16" t="n">
+      <c r="G16" s="4">
         <v>46.86</v>
       </c>
-      <c r="E16" t="n">
+      <c r="H16" s="4">
         <v>46.9</v>
       </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n">
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A17" s="2">
         <v>46127</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17" s="2">
+        <v>46127</v>
+      </c>
+      <c r="C17" s="1">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="D17" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E17" s="4">
         <v>49.44</v>
       </c>
-      <c r="C17" t="n">
+      <c r="F17" s="4">
         <v>49.67</v>
       </c>
-      <c r="D17" t="n">
+      <c r="G17" s="4">
         <v>48.05</v>
       </c>
-      <c r="E17" t="n">
+      <c r="H17" s="4">
         <v>48.05</v>
       </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n">
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A18" s="2">
         <v>46128</v>
       </c>
-      <c r="B18" t="n">
+      <c r="B18" s="2">
+        <v>46128</v>
+      </c>
+      <c r="C18" s="1">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="D18" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E18" s="4">
         <v>48.66</v>
       </c>
-      <c r="C18" t="n">
+      <c r="F18" s="4">
         <v>49.33</v>
       </c>
-      <c r="D18" t="n">
+      <c r="G18" s="4">
         <v>48.01</v>
       </c>
-      <c r="E18" t="n">
+      <c r="H18" s="4">
         <v>49.13</v>
       </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n">
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A19" s="2">
         <v>46129</v>
       </c>
-      <c r="B19" t="n">
+      <c r="B19" s="2">
+        <v>46129</v>
+      </c>
+      <c r="C19" s="1">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="D19" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E19" s="4">
         <v>49.48</v>
       </c>
-      <c r="C19" t="n">
+      <c r="F19" s="4">
         <v>50.07</v>
       </c>
-      <c r="D19" t="n">
+      <c r="G19" s="4">
         <v>47.8</v>
       </c>
-      <c r="E19" t="n">
+      <c r="H19" s="4">
         <v>47.92</v>
       </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n">
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A20" s="2">
         <v>46132</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B20" s="2">
+        <v>46132</v>
+      </c>
+      <c r="C20" s="1">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="D20" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E20" s="4">
         <v>48.91</v>
       </c>
-      <c r="C20" t="n">
+      <c r="F20" s="4">
         <v>49.75</v>
       </c>
-      <c r="D20" t="n">
+      <c r="G20" s="4">
         <v>48.17</v>
       </c>
-      <c r="E20" t="n">
+      <c r="H20" s="4">
         <v>49.69</v>
       </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n">
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A21" s="2">
         <v>46133</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B21" s="2">
+        <v>46133</v>
+      </c>
+      <c r="C21" s="1">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="D21" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E21" s="4">
         <v>49.87</v>
       </c>
-      <c r="C21" t="n">
+      <c r="F21" s="4">
         <v>49.92</v>
       </c>
-      <c r="D21" t="n">
+      <c r="G21" s="4">
         <v>48.39</v>
       </c>
-      <c r="E21" t="n">
+      <c r="H21" s="4">
         <v>48.4</v>
       </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="n">
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A22" s="2">
         <v>46134</v>
       </c>
-      <c r="B22" t="n">
+      <c r="B22" s="2">
+        <v>46134</v>
+      </c>
+      <c r="C22" s="1">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="D22" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E22" s="4">
         <v>48.27</v>
       </c>
-      <c r="C22" t="n">
+      <c r="F22" s="4">
         <v>50.43</v>
       </c>
-      <c r="D22" t="n">
+      <c r="G22" s="4">
         <v>48.13</v>
       </c>
-      <c r="E22" t="n">
+      <c r="H22" s="4">
         <v>48.31</v>
       </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n">
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A23" s="2">
         <v>46135</v>
       </c>
-      <c r="B23" t="n">
+      <c r="B23" s="2">
+        <v>46135</v>
+      </c>
+      <c r="C23" s="1">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="D23" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E23" s="4">
         <v>49.03</v>
       </c>
-      <c r="C23" t="n">
+      <c r="F23" s="4">
         <v>50.52</v>
       </c>
-      <c r="D23" t="n">
+      <c r="G23" s="4">
         <v>48.31</v>
       </c>
-      <c r="E23" t="n">
+      <c r="H23" s="4">
         <v>48.57</v>
       </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n">
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A24" s="2">
         <v>46136</v>
       </c>
-      <c r="B24" t="n">
+      <c r="B24" s="2">
+        <v>46136</v>
+      </c>
+      <c r="C24" s="1">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="D24" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E24" s="4">
         <v>46.88</v>
       </c>
-      <c r="C24" t="n">
+      <c r="F24" s="4">
         <v>48.58</v>
       </c>
-      <c r="D24" t="n">
+      <c r="G24" s="4">
         <v>46.68</v>
       </c>
-      <c r="E24" t="n">
+      <c r="H24" s="4">
         <v>47.79</v>
       </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="n">
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A25" s="2">
         <v>46139</v>
       </c>
-      <c r="B25" t="n">
+      <c r="B25" s="2">
+        <v>46139</v>
+      </c>
+      <c r="C25" s="1">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="D25" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E25" s="4">
         <v>46.83</v>
       </c>
-      <c r="C25" t="n">
+      <c r="F25" s="4">
         <v>48.02</v>
       </c>
-      <c r="D25" t="n">
+      <c r="G25" s="4">
         <v>46.63</v>
       </c>
-      <c r="E25" t="n">
+      <c r="H25" s="4">
         <v>47</v>
       </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="n">
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A26" s="2">
         <v>46140</v>
       </c>
-      <c r="B26" t="n">
+      <c r="B26" s="2">
+        <v>46140</v>
+      </c>
+      <c r="C26" s="1">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="D26" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E26" s="4">
         <v>46.43</v>
       </c>
-      <c r="C26" t="n">
+      <c r="F26" s="4">
         <v>48.14</v>
       </c>
-      <c r="D26" t="n">
+      <c r="G26" s="4">
         <v>46.38</v>
       </c>
-      <c r="E26" t="n">
+      <c r="H26" s="4">
         <v>47.7</v>
       </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="n">
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A27" s="2">
         <v>46141</v>
       </c>
-      <c r="B27" t="n">
+      <c r="B27" s="2">
+        <v>46141</v>
+      </c>
+      <c r="C27" s="1">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="D27" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E27" s="4">
         <v>46.37</v>
       </c>
-      <c r="C27" t="n">
+      <c r="F27" s="4">
         <v>47.08</v>
       </c>
-      <c r="D27" t="n">
+      <c r="G27" s="4">
         <v>44.06</v>
       </c>
-      <c r="E27" t="n">
+      <c r="H27" s="4">
         <v>45.16</v>
       </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="n">
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A28" s="2">
         <v>46142</v>
       </c>
-      <c r="B28" t="n">
+      <c r="B28" s="2">
+        <v>46142</v>
+      </c>
+      <c r="C28" s="1">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="D28" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E28" s="4">
         <v>45.36</v>
       </c>
-      <c r="C28" t="n">
+      <c r="F28" s="4">
         <v>46.08</v>
       </c>
-      <c r="D28" t="n">
+      <c r="G28" s="4">
         <v>44.81</v>
       </c>
-      <c r="E28" t="n">
+      <c r="H28" s="4">
         <v>44.91</v>
       </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="n">
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A29" s="2">
         <v>46143</v>
       </c>
-      <c r="B29" t="n">
+      <c r="B29" s="2">
+        <v>46143</v>
+      </c>
+      <c r="C29" s="1">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="D29" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E29" s="4">
         <v>43.89</v>
       </c>
-      <c r="C29" t="n">
+      <c r="F29" s="4">
         <v>45.28</v>
       </c>
-      <c r="D29" t="n">
+      <c r="G29" s="4">
         <v>43.05</v>
       </c>
-      <c r="E29" t="n">
+      <c r="H29" s="4">
         <v>43.16</v>
       </c>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="n">
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A30" s="2">
         <v>46146</v>
       </c>
-      <c r="B30" t="n">
+      <c r="B30" s="2">
+        <v>46146</v>
+      </c>
+      <c r="C30" s="1">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="D30" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E30" s="4">
         <v>46.57</v>
       </c>
-      <c r="C30" t="n">
+      <c r="F30" s="4">
         <v>46.82</v>
       </c>
-      <c r="D30" t="n">
+      <c r="G30" s="4">
         <v>44.11</v>
       </c>
-      <c r="E30" t="n">
+      <c r="H30" s="4">
         <v>44.16</v>
       </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="n">
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A31" s="2">
         <v>46147</v>
       </c>
-      <c r="B31" t="n">
+      <c r="B31" s="2">
+        <v>46147</v>
+      </c>
+      <c r="C31" s="1">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="D31" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E31" s="4">
         <v>45.62</v>
       </c>
-      <c r="C31" t="n">
+      <c r="F31" s="4">
         <v>46.73</v>
       </c>
-      <c r="D31" t="n">
+      <c r="G31" s="4">
         <v>45.01</v>
       </c>
-      <c r="E31" t="n">
+      <c r="H31" s="4">
         <v>45.34</v>
       </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="n">
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A32" s="2">
         <v>46148</v>
       </c>
-      <c r="B32" t="n">
+      <c r="B32" s="2">
+        <v>46148</v>
+      </c>
+      <c r="C32" s="1">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="D32" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E32" s="4">
         <v>45.02</v>
       </c>
-      <c r="C32" t="n">
+      <c r="F32" s="4">
         <v>46.45</v>
       </c>
-      <c r="D32" t="n">
+      <c r="G32" s="4">
         <v>44.35</v>
       </c>
-      <c r="E32" t="n">
+      <c r="H32" s="4">
         <v>45.69</v>
       </c>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="n">
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A33" s="2">
         <v>46149</v>
       </c>
-      <c r="B33" t="n">
+      <c r="B33" s="2">
+        <v>46149</v>
+      </c>
+      <c r="C33" s="1">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="D33" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E33" s="4">
         <v>44.91</v>
       </c>
-      <c r="C33" t="n">
+      <c r="F33" s="4">
         <v>51.11</v>
       </c>
-      <c r="D33" t="n">
+      <c r="G33" s="4">
         <v>43.21</v>
       </c>
-      <c r="E33" t="n">
+      <c r="H33" s="4">
         <v>44.28</v>
       </c>
-      <c r="F33" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="n">
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A34" s="2">
         <v>46150</v>
       </c>
-      <c r="B34" t="n">
+      <c r="B34" s="2">
+        <v>46150</v>
+      </c>
+      <c r="C34" s="1">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="D34" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E34" s="4">
         <v>43.33</v>
       </c>
-      <c r="C34" t="n">
+      <c r="F34" s="4">
         <v>44.12</v>
       </c>
-      <c r="D34" t="n">
+      <c r="G34" s="4">
         <v>42.19</v>
       </c>
-      <c r="E34" t="n">
+      <c r="H34" s="4">
         <v>43.13</v>
       </c>
-      <c r="F34" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="n">
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A35" s="2">
         <v>46153</v>
       </c>
-      <c r="B35" t="n">
+      <c r="B35" s="2">
+        <v>46153</v>
+      </c>
+      <c r="C35" s="1">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="D35" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E35" s="4">
         <v>43.24</v>
       </c>
-      <c r="C35" t="n">
+      <c r="F35" s="4">
         <v>44.19</v>
       </c>
-      <c r="D35" t="n">
+      <c r="G35" s="4">
         <v>41.53</v>
       </c>
-      <c r="E35" t="n">
+      <c r="H35" s="4">
         <v>43.07</v>
       </c>
-      <c r="F35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="n">
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A36" s="2">
         <v>46154</v>
       </c>
-      <c r="B36" t="n">
+      <c r="B36" s="2">
+        <v>46154</v>
+      </c>
+      <c r="C36" s="1">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="D36" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E36" s="4">
         <v>43.49</v>
       </c>
-      <c r="C36" t="n">
+      <c r="F36" s="4">
         <v>44.45</v>
       </c>
-      <c r="D36" t="n">
+      <c r="G36" s="4">
         <v>43.26</v>
       </c>
-      <c r="E36" t="n">
+      <c r="H36" s="4">
         <v>43.71</v>
       </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="n">
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A37" s="2">
         <v>46155</v>
       </c>
-      <c r="B37" t="n">
+      <c r="B37" s="2">
+        <v>46155</v>
+      </c>
+      <c r="C37" s="1">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="D37" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E37" s="4">
         <v>43.93</v>
       </c>
-      <c r="C37" t="n">
+      <c r="F37" s="4">
         <v>44.32</v>
       </c>
-      <c r="D37" t="n">
+      <c r="G37" s="4">
         <v>43.29</v>
       </c>
-      <c r="E37" t="n">
+      <c r="H37" s="4">
         <v>43.49</v>
       </c>
-      <c r="F37" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="n">
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A38" s="2">
         <v>46156</v>
       </c>
-      <c r="B38" t="n">
+      <c r="B38" s="2">
+        <v>46156</v>
+      </c>
+      <c r="C38" s="1">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="D38" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E38" s="4">
         <v>43.34</v>
       </c>
-      <c r="C38" t="n">
+      <c r="F38" s="4">
         <v>44.47</v>
       </c>
-      <c r="D38" t="n">
+      <c r="G38" s="4">
         <v>43.25</v>
       </c>
-      <c r="E38" t="n">
+      <c r="H38" s="4">
         <v>44.36</v>
       </c>
-      <c r="F38" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="n">
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A39" s="2">
         <v>46157</v>
       </c>
-      <c r="B39" t="n">
+      <c r="B39" s="2">
+        <v>46157</v>
+      </c>
+      <c r="C39" s="1">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="D39" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E39" s="4">
         <v>42.61</v>
       </c>
-      <c r="C39" t="n">
+      <c r="F39" s="4">
         <v>45.14</v>
       </c>
-      <c r="D39" t="n">
+      <c r="G39" s="4">
         <v>42.53</v>
       </c>
-      <c r="E39" t="n">
+      <c r="H39" s="4">
         <v>43.63</v>
       </c>
-      <c r="F39" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="n">
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A40" s="2">
         <v>46160</v>
       </c>
-      <c r="B40" t="n">
+      <c r="B40" s="2">
+        <v>46160</v>
+      </c>
+      <c r="C40" s="1">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="D40" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E40" s="4">
         <v>43.8</v>
       </c>
-      <c r="C40" t="n">
+      <c r="F40" s="4">
         <v>45.35</v>
       </c>
-      <c r="D40" t="n">
+      <c r="G40" s="4">
         <v>43.73</v>
       </c>
-      <c r="E40" t="n">
+      <c r="H40" s="4">
         <v>44.69</v>
       </c>
-      <c r="F40" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="n">
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A41" s="2">
         <v>46161</v>
       </c>
-      <c r="B41" t="n">
+      <c r="B41" s="2">
+        <v>46161</v>
+      </c>
+      <c r="C41" s="1">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="D41" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E41" s="4">
         <v>43.56</v>
       </c>
-      <c r="C41" t="n">
+      <c r="F41" s="4">
         <v>44.87</v>
       </c>
-      <c r="D41" t="n">
+      <c r="G41" s="4">
         <v>43.4</v>
       </c>
-      <c r="E41" t="n">
+      <c r="H41" s="4">
         <v>44.87</v>
       </c>
-      <c r="F41" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="n">
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A42" s="2">
         <v>46162</v>
       </c>
-      <c r="B42" t="n">
+      <c r="B42" s="2">
+        <v>46162</v>
+      </c>
+      <c r="C42" s="1">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="D42" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E42" s="4">
         <v>42.58</v>
       </c>
-      <c r="C42" t="n">
+      <c r="F42" s="4">
         <v>43.87</v>
       </c>
-      <c r="D42" t="n">
+      <c r="G42" s="4">
         <v>42.12</v>
       </c>
-      <c r="E42" t="n">
+      <c r="H42" s="4">
         <v>43.4</v>
       </c>
-      <c r="F42" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="n">
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A43" s="2">
         <v>46163</v>
       </c>
-      <c r="B43" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="C43" t="n">
+      <c r="B43" s="2">
+        <v>46163</v>
+      </c>
+      <c r="C43" s="1">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="D43" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E43" s="4">
+        <v>40.299999999999997</v>
+      </c>
+      <c r="F43" s="4">
         <v>42.69</v>
       </c>
-      <c r="D43" t="n">
+      <c r="G43" s="4">
         <v>40.03</v>
       </c>
-      <c r="E43" t="n">
+      <c r="H43" s="4">
         <v>42.02</v>
       </c>
-      <c r="F43" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="n">
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A44" s="2">
         <v>46164</v>
       </c>
-      <c r="B44" t="n">
+      <c r="B44" s="2">
+        <v>46164</v>
+      </c>
+      <c r="C44" s="1">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="D44" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E44" s="4">
         <v>40.11</v>
       </c>
-      <c r="C44" t="n">
+      <c r="F44" s="4">
         <v>40.42</v>
       </c>
-      <c r="D44" t="n">
-        <v>39.2</v>
-      </c>
-      <c r="E44" t="n">
+      <c r="G44" s="4">
+        <v>39.200000000000003</v>
+      </c>
+      <c r="H44" s="4">
         <v>39.89</v>
       </c>
-      <c r="F44" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="n">
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A45" s="2">
         <v>46168</v>
       </c>
-      <c r="B45" t="n">
+      <c r="B45" s="2">
+        <v>46168</v>
+      </c>
+      <c r="C45" s="1">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="D45" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E45" s="4">
         <v>52.92</v>
       </c>
-      <c r="C45" t="n">
+      <c r="F45" s="4">
         <v>53.55</v>
       </c>
-      <c r="D45" t="n">
-        <v>38.91</v>
-      </c>
-      <c r="E45" t="n">
+      <c r="G45" s="4">
+        <v>38.909999999999997</v>
+      </c>
+      <c r="H45" s="4">
         <v>44.48</v>
       </c>
-      <c r="F45" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="n">
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A46" s="2">
         <v>46169</v>
       </c>
-      <c r="B46" t="n">
+      <c r="B46" s="2">
+        <v>46169</v>
+      </c>
+      <c r="C46" s="1">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="D46" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E46" s="4">
         <v>41.49</v>
       </c>
-      <c r="C46" t="n">
+      <c r="F46" s="4">
         <v>50.58</v>
       </c>
-      <c r="D46" t="n">
-        <v>40.77</v>
-      </c>
-      <c r="E46" t="n">
+      <c r="G46" s="4">
+        <v>40.770000000000003</v>
+      </c>
+      <c r="H46" s="4">
         <v>44.3</v>
       </c>
-      <c r="F46" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="n">
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A47" s="2">
         <v>46170</v>
       </c>
-      <c r="B47" t="n">
+      <c r="B47" s="2">
+        <v>46170</v>
+      </c>
+      <c r="C47" s="1">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="D47" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E47" s="4">
         <v>41.5</v>
       </c>
-      <c r="C47" t="n">
+      <c r="F47" s="4">
         <v>50.54</v>
       </c>
-      <c r="D47" t="n">
+      <c r="G47" s="4">
         <v>38.92</v>
       </c>
-      <c r="E47" t="n">
+      <c r="H47" s="4">
         <v>41.36</v>
       </c>
-      <c r="F47" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="n">
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A48" s="2">
         <v>46171</v>
       </c>
-      <c r="B48" t="n">
+      <c r="B48" s="2">
+        <v>46171</v>
+      </c>
+      <c r="C48" s="1">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="D48" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E48" s="4">
         <v>41.09</v>
       </c>
-      <c r="C48" t="n">
+      <c r="F48" s="4">
         <v>45.48</v>
       </c>
-      <c r="D48" t="n">
+      <c r="G48" s="4">
         <v>40.81</v>
       </c>
-      <c r="E48" t="n">
+      <c r="H48" s="4">
         <v>44.63</v>
-      </c>
-      <c r="F48" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>